--- a/data/trans_orig/P33B_R5-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R5-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37492</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27864</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>40419</t>
+          <t>46246</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>31533</t>
+          <t>35797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51265</t>
+          <t>57746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77910</t>
+          <t>85843</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62579</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>103388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>467720</t>
+          <t>511021</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455298</t>
+          <t>499349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>477348</t>
+          <t>521555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>407048</t>
+          <t>442165</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>396202</t>
+          <t>430665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415934</t>
+          <t>452614</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>874769</t>
+          <t>953186</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>859114</t>
+          <t>935641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>890100</t>
+          <t>968815</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,24%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>32012</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42068</t>
+          <t>42674</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26411</t>
+          <t>31461</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35700</t>
+          <t>40873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>56886</t>
+          <t>63473</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45433</t>
+          <t>51318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69145</t>
+          <t>80061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421738</t>
+          <t>451200</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410145</t>
+          <t>440538</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430243</t>
+          <t>460202</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>355579</t>
+          <t>391013</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>346290</t>
+          <t>381601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>362788</t>
+          <t>399445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>777317</t>
+          <t>842213</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>765058</t>
+          <t>825625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>788770</t>
+          <t>854368</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>37462</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>27940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61244</t>
+          <t>50261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25056</t>
+          <t>27724</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>19533</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32868</t>
+          <t>35407</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>60084</t>
+          <t>65186</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>53011</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89665</t>
+          <t>79553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>633237</t>
+          <t>434150</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607020</t>
+          <t>421351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>655897</t>
+          <t>443672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>159773</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>134043</t>
+          <t>152090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>148840</t>
+          <t>167964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>775091</t>
+          <t>593923</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>745510</t>
+          <t>579556</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>809205</t>
+          <t>606098</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>88311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64348</t>
+          <t>73632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98056</t>
+          <t>109928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>70518</t>
+          <t>78520</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34624</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94382</t>
+          <t>94310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>149860</t>
+          <t>166831</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104614</t>
+          <t>145330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176274</t>
+          <t>190725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>955478</t>
+          <t>1043532</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>936763</t>
+          <t>1021915</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>970471</t>
+          <t>1058211</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>907010</t>
+          <t>782095</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>883146</t>
+          <t>766305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>942904</t>
+          <t>795352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1862487</t>
+          <t>1825627</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1836073</t>
+          <t>1801733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907733</t>
+          <t>1847128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>92,71%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27255</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>21577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>134938</t>
+          <t>145827</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102389</t>
+          <t>129601</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163565</t>
+          <t>163688</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>162192</t>
+          <t>176470</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131410</t>
+          <t>158724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>186284</t>
+          <t>198755</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>445764</t>
+          <t>535251</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>435151</t>
+          <t>524381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>453082</t>
+          <t>544317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>704058</t>
+          <t>684300</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>675431</t>
+          <t>666439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>736607</t>
+          <t>700526</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1149823</t>
+          <t>1219552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1125731</t>
+          <t>1197267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1180605</t>
+          <t>1237298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22378</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>123396</t>
+          <t>136225</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>118876</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139971</t>
+          <t>153937</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>130327</t>
+          <t>142679</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112651</t>
+          <t>123967</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>148478</t>
+          <t>164723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>233576</t>
+          <t>230774</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218129</t>
+          <t>216808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238297</t>
+          <t>235128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>637975</t>
+          <t>708056</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>621400</t>
+          <t>690344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654472</t>
+          <t>725405</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>871551</t>
+          <t>938830</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>853400</t>
+          <t>916786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>889227</t>
+          <t>957542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>216521</t>
+          <t>234479</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166082</t>
+          <t>209071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>249038</t>
+          <t>267818</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>420737</t>
+          <t>466003</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>333661</t>
+          <t>431744</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>465887</t>
+          <t>498573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>637258</t>
+          <t>700482</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>541236</t>
+          <t>657490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>694106</t>
+          <t>743702</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3157513</t>
+          <t>3205928</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3124996</t>
+          <t>3172589</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3207952</t>
+          <t>3231336</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3153526</t>
+          <t>3167403</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3108376</t>
+          <t>3134833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3240602</t>
+          <t>3201662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6311039</t>
+          <t>6373330</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6254191</t>
+          <t>6330110</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6407061</t>
+          <t>6416322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
